--- a/CustomModel/L5.xlsx
+++ b/CustomModel/L5.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="4">
   <si>
     <t>E5</t>
   </si>
@@ -90,7 +90,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -109,6 +109,15 @@
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -421,14 +430,14 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="8" width="5.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="8" width="5.576428571428571" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="8" width="6.2907142857142855" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="9" width="6.005" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="10" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="11" width="5.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="11" width="5.576428571428571" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="11" width="6.2907142857142855" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="12" width="6.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="21">
@@ -489,7 +498,7 @@
       </c>
       <c r="E4" s="5"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="20.25">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
@@ -503,6 +512,74 @@
         <v>3</v>
       </c>
       <c r="E5" s="5"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="7">
+        <v>1.41</v>
+      </c>
+      <c r="C6" s="7">
+        <v>1.2</v>
+      </c>
+      <c r="D6" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="E6" s="8">
+        <v>7</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
+      <c r="A7" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="7">
+        <v>6.71</v>
+      </c>
+      <c r="C7" s="7">
+        <v>17</v>
+      </c>
+      <c r="D7" s="7">
+        <v>0</v>
+      </c>
+      <c r="E7" s="9">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
+      <c r="A8" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" s="7">
+        <v>5.49</v>
+      </c>
+      <c r="C8" s="7">
+        <v>0.8</v>
+      </c>
+      <c r="D8" s="7">
+        <v>6</v>
+      </c>
+      <c r="E8" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="21">
+      <c r="A9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="4">
+        <v>3.08</v>
+      </c>
+      <c r="C9" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="D9" s="4">
+        <v>7.88</v>
+      </c>
+      <c r="E9" s="8">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
